--- a/data/attendance/ECOLE_نذير_2_ثانوي.xlsx
+++ b/data/attendance/ECOLE_نذير_2_ثانوي.xlsx
@@ -48,147 +48,231 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
+          <t>student_id:6eb5e29c-8e60-4130-af22-5e34fdd483a4</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0">
+      <text>
+        <r>
           <t>student_id:6d73674c-ee22-4fff-ae51-4097a92cc46a</t>
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0">
+    <comment ref="B11" authorId="0">
       <text>
         <r>
           <t>student_id:fee82d60-5d8e-4c94-a0d5-86a356c9c63a</t>
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0">
+    <comment ref="B12" authorId="0">
       <text>
         <r>
           <t>student_id:22ec7f6e-72e9-4cc2-be55-83873924801b</t>
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <t>student_id:310ae1b6-8df5-40ff-bbb6-b2ddc91f4571</t>
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0">
+    <comment ref="B14" authorId="0">
       <text>
         <r>
           <t>student_id:77bd56fb-fbda-4b39-8188-71ef2962750e</t>
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0">
+    <comment ref="B15" authorId="0">
       <text>
         <r>
           <t>student_id:d730ae9f-aaab-4df5-8dd1-e9d39eb92a39</t>
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <t>student_id:11ca1679-ab61-464a-b923-80842dd79263</t>
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0">
+    <comment ref="B17" authorId="0">
       <text>
         <r>
           <t>student_id:7946d5a6-e4cc-4c0d-b82f-9761f7d29c33</t>
         </r>
       </text>
     </comment>
-    <comment ref="B17" authorId="0">
+    <comment ref="B18" authorId="0">
       <text>
         <r>
           <t>student_id:3cbe4506-902d-4820-9a2d-c6e02a352fe3</t>
         </r>
       </text>
     </comment>
-    <comment ref="B18" authorId="0">
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <t>student_id:3f594873-c587-4811-a489-04a4b568a731</t>
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0">
+    <comment ref="B20" authorId="0">
       <text>
         <r>
           <t>student_id:2f4a5bda-2c3f-4fe6-a75a-9d434fc7a4a9</t>
         </r>
       </text>
     </comment>
-    <comment ref="B20" authorId="0">
+    <comment ref="B21" authorId="0">
       <text>
         <r>
           <t>student_id:0868ba6a-87e5-4a00-8ee4-2b8134a90d2d</t>
         </r>
       </text>
     </comment>
-    <comment ref="B21" authorId="0">
+    <comment ref="B22" authorId="0">
       <text>
         <r>
           <t>student_id:4a028e2f-fcf8-4e29-ad76-dfea7b4de0e2</t>
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0">
+    <comment ref="B23" authorId="0">
       <text>
         <r>
           <t>student_id:3a376a76-0310-42d0-a510-1d22a2c41985</t>
         </r>
       </text>
     </comment>
-    <comment ref="B23" authorId="0">
+    <comment ref="B24" authorId="0">
       <text>
         <r>
           <t>student_id:f9df5677-74e4-4d43-87be-48228f5f9e73</t>
         </r>
       </text>
     </comment>
-    <comment ref="B24" authorId="0">
+    <comment ref="B25" authorId="0">
       <text>
         <r>
           <t>student_id:ecf8816b-f12f-4890-bc1a-f921b391c511</t>
         </r>
       </text>
     </comment>
-    <comment ref="B25" authorId="0">
+    <comment ref="B26" authorId="0">
       <text>
         <r>
           <t>student_id:cafa7466-0167-42a7-af93-ac823bda60b4</t>
         </r>
       </text>
     </comment>
-    <comment ref="B26" authorId="0">
+    <comment ref="B27" authorId="0">
       <text>
         <r>
           <t>student_id:69063dd4-9a55-4330-b2df-e08fff44f0b6</t>
         </r>
       </text>
     </comment>
-    <comment ref="B27" authorId="0">
+    <comment ref="B28" authorId="0">
       <text>
         <r>
           <t>student_id:5cc61b73-db6c-4ecb-9597-e645001f2318</t>
         </r>
       </text>
     </comment>
-    <comment ref="B28" authorId="0">
+    <comment ref="B29" authorId="0">
       <text>
         <r>
           <t>student_id:0a142c16-9ba0-4444-a2f6-b2ca1e13d1dc</t>
         </r>
       </text>
     </comment>
-    <comment ref="B29" authorId="0">
+    <comment ref="B30" authorId="0">
       <text>
         <r>
           <t>student_id:977ad25d-436c-4f38-9e82-8f5c14ffb6d2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0">
+      <text>
+        <r>
+          <t>student_id:e142d54a-19d1-4aea-b2be-47a4c6d353cd</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0">
+      <text>
+        <r>
+          <t>student_id:3bcce919-98b0-44f3-abc2-2b25bc8113ff</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0">
+      <text>
+        <r>
+          <t>student_id:bd59156d-3414-423d-98bd-88d35ded3807</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0">
+      <text>
+        <r>
+          <t>student_id:7adfd15a-ff08-465e-b054-85db0fed0421</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0">
+      <text>
+        <r>
+          <t>student_id:a87e03cf-aed6-4c60-a440-70cf1a48c123</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0">
+      <text>
+        <r>
+          <t>student_id:31c15a13-aa3e-42f6-b8df-11127786213d</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0">
+      <text>
+        <r>
+          <t>student_id:f90909b6-1211-4608-bebf-6ed3e9020c9a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0">
+      <text>
+        <r>
+          <t>student_id:a99c0813-9233-4d20-aa2e-23dde03ef407</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0">
+      <text>
+        <r>
+          <t>student_id:fb132527-132c-4986-8653-8d03e86be555</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0">
+      <text>
+        <r>
+          <t>student_id:85e1c413-fc35-4711-a26a-c82d31f4063e</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0">
+      <text>
+        <r>
+          <t>student_id:79bf5bc8-8fa4-40fd-9609-58d6d0cd176a</t>
         </r>
       </text>
     </comment>
@@ -197,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
   <si>
     <t>نذير 2 ثانوي  |  ECOLE  |  2AS  |  بوعبدالله نذير</t>
   </si>
@@ -211,6 +295,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -220,6 +307,9 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -235,6 +325,9 @@
     <t>حماني نسرين</t>
   </si>
   <si>
+    <t>خنيو لجين</t>
+  </si>
+  <si>
     <t>غميرد مريم</t>
   </si>
   <si>
@@ -298,6 +391,39 @@
     <t>شاقو سارة</t>
   </si>
   <si>
+    <t>سيود تسنيم</t>
+  </si>
+  <si>
+    <t>بوالعتروس نيروز</t>
+  </si>
+  <si>
+    <t>ميعوات انفال</t>
+  </si>
+  <si>
+    <t>ميلي سيرين</t>
+  </si>
+  <si>
+    <t>لعروس اية</t>
+  </si>
+  <si>
+    <t>بوزياني ياسمين</t>
+  </si>
+  <si>
+    <t>عبدلي عبد الرحمن</t>
+  </si>
+  <si>
+    <t>شاقور تاج الدين</t>
+  </si>
+  <si>
+    <t>زمار محمد لمين</t>
+  </si>
+  <si>
+    <t>كردون جنان</t>
+  </si>
+  <si>
+    <t>شايب اماني</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -325,7 +451,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -815,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -841,7 +970,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -851,10 +980,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -896,46 +1028,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -943,7 +1075,7 @@
         <v>378</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -987,7 +1119,7 @@
         <v>379</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -1031,7 +1163,7 @@
         <v>380</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -1075,7 +1207,7 @@
         <v>387</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -1116,10 +1248,10 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>718</v>
+        <v>453</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -1160,10 +1292,10 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1204,10 +1336,10 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -1248,10 +1380,10 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" s="9">
         <v>0</v>
@@ -1292,10 +1424,10 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -1336,10 +1468,10 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C14" s="9">
         <v>0</v>
@@ -1380,10 +1512,10 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" s="8">
         <v>0</v>
@@ -1424,10 +1556,10 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C16" s="9">
         <v>0</v>
@@ -1468,10 +1600,10 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C17" s="8">
         <v>0</v>
@@ -1512,10 +1644,10 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C18" s="9">
         <v>0</v>
@@ -1556,10 +1688,10 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C19" s="8">
         <v>0</v>
@@ -1600,10 +1732,10 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C20" s="9">
         <v>0</v>
@@ -1644,10 +1776,10 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C21" s="8">
         <v>0</v>
@@ -1688,10 +1820,10 @@
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C22" s="9">
         <v>0</v>
@@ -1732,10 +1864,10 @@
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C23" s="8">
         <v>0</v>
@@ -1776,10 +1908,10 @@
     </row>
     <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C24" s="9">
         <v>0</v>
@@ -1820,10 +1952,10 @@
     </row>
     <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C25" s="8">
         <v>0</v>
@@ -1864,10 +1996,10 @@
     </row>
     <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C26" s="9">
         <v>0</v>
@@ -1908,10 +2040,10 @@
     </row>
     <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C27" s="8">
         <v>0</v>
@@ -1952,10 +2084,10 @@
     </row>
     <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C28" s="9">
         <v>0</v>
@@ -1996,45 +2128,573 @@
     </row>
     <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
+        <v>737</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
         <v>738</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0</v>
-      </c>
-      <c r="F29" s="8">
-        <v>0</v>
-      </c>
-      <c r="G29" s="8">
-        <v>0</v>
-      </c>
-      <c r="H29" s="8">
-        <v>0</v>
-      </c>
-      <c r="I29" s="8">
-        <v>0</v>
-      </c>
-      <c r="J29" s="8">
-        <v>0</v>
-      </c>
-      <c r="K29" s="8">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8">
-        <v>0</v>
-      </c>
-      <c r="M29" s="8">
-        <v>0</v>
-      </c>
-      <c r="N29" s="8">
+      <c r="B30" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="9">
+        <v>0</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
+      <c r="J30" s="9">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9">
+        <v>0</v>
+      </c>
+      <c r="M30" s="9">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>875</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0</v>
+      </c>
+      <c r="M31" s="8">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>877</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9">
+        <v>0</v>
+      </c>
+      <c r="M32" s="9">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>880</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>882</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="9">
+        <v>0</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9">
+        <v>0</v>
+      </c>
+      <c r="L34" s="9">
+        <v>0</v>
+      </c>
+      <c r="M34" s="9">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>884</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0</v>
+      </c>
+      <c r="D35" s="8">
+        <v>0</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0</v>
+      </c>
+      <c r="H35" s="8">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8">
+        <v>0</v>
+      </c>
+      <c r="M35" s="8">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>886</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="9">
+        <v>0</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0</v>
+      </c>
+      <c r="H36" s="9">
+        <v>0</v>
+      </c>
+      <c r="I36" s="9">
+        <v>0</v>
+      </c>
+      <c r="J36" s="9">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9">
+        <v>0</v>
+      </c>
+      <c r="M36" s="9">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>887</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="8">
+        <v>0</v>
+      </c>
+      <c r="D37" s="8">
+        <v>0</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8">
+        <v>0</v>
+      </c>
+      <c r="H37" s="8">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8">
+        <v>0</v>
+      </c>
+      <c r="M37" s="8">
+        <v>0</v>
+      </c>
+      <c r="N37" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>888</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9">
+        <v>0</v>
+      </c>
+      <c r="I38" s="9">
+        <v>0</v>
+      </c>
+      <c r="J38" s="9">
+        <v>0</v>
+      </c>
+      <c r="K38" s="9">
+        <v>0</v>
+      </c>
+      <c r="L38" s="9">
+        <v>0</v>
+      </c>
+      <c r="M38" s="9">
+        <v>0</v>
+      </c>
+      <c r="N38" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>889</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="8">
+        <v>0</v>
+      </c>
+      <c r="D39" s="8">
+        <v>0</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8">
+        <v>0</v>
+      </c>
+      <c r="H39" s="8">
+        <v>0</v>
+      </c>
+      <c r="I39" s="8">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8">
+        <v>0</v>
+      </c>
+      <c r="K39" s="8">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8">
+        <v>0</v>
+      </c>
+      <c r="M39" s="8">
+        <v>0</v>
+      </c>
+      <c r="N39" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>890</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="9">
+        <v>0</v>
+      </c>
+      <c r="D40" s="9">
+        <v>0</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9">
+        <v>0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>0</v>
+      </c>
+      <c r="I40" s="9">
+        <v>0</v>
+      </c>
+      <c r="J40" s="9">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9">
+        <v>0</v>
+      </c>
+      <c r="L40" s="9">
+        <v>0</v>
+      </c>
+      <c r="M40" s="9">
+        <v>0</v>
+      </c>
+      <c r="N40" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>891</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="8">
+        <v>0</v>
+      </c>
+      <c r="D41" s="8">
+        <v>0</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8">
+        <v>0</v>
+      </c>
+      <c r="H41" s="8">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8">
+        <v>0</v>
+      </c>
+      <c r="M41" s="8">
+        <v>0</v>
+      </c>
+      <c r="N41" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2054,7 +2714,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -2062,77 +2722,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
